--- a/reports/Debug-snowbowl-20251230/For Winter Ending (Prior Year)_Visits.xlsx
+++ b/reports/Debug-snowbowl-20251230/For Winter Ending (Prior Year)_Visits.xlsx
@@ -434,7 +434,7 @@
         <v>45604</v>
       </c>
       <c r="C2" s="2">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -448,7 +448,7 @@
         <v>45604</v>
       </c>
       <c r="C3" s="2">
-        <v>1</v>
+        <v>789</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>5</v>
@@ -459,10 +459,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="2">
-        <v>45604</v>
+        <v>45605</v>
       </c>
       <c r="C4" s="2">
-        <v>139</v>
+        <v>237</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>6</v>
@@ -473,13 +473,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="2">
-        <v>45607</v>
+        <v>45606</v>
       </c>
       <c r="C5" s="2">
-        <v>473</v>
+        <v>4</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -487,13 +487,13 @@
         <v>1</v>
       </c>
       <c r="B6" s="2">
-        <v>45608</v>
+        <v>45607</v>
       </c>
       <c r="C6" s="2">
-        <v>3</v>
+        <v>904</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -501,13 +501,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="2">
-        <v>45610</v>
+        <v>45609</v>
       </c>
       <c r="C7" s="2">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -515,10 +515,10 @@
         <v>1</v>
       </c>
       <c r="B8" s="2">
-        <v>45611</v>
+        <v>45616</v>
       </c>
       <c r="C8" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>7</v>
@@ -529,13 +529,13 @@
         <v>1</v>
       </c>
       <c r="B9" s="2">
-        <v>45613</v>
+        <v>45619</v>
       </c>
       <c r="C9" s="2">
-        <v>468</v>
+        <v>77</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -543,13 +543,13 @@
         <v>1</v>
       </c>
       <c r="B10" s="2">
-        <v>45614</v>
+        <v>45622</v>
       </c>
       <c r="C10" s="2">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -557,13 +557,13 @@
         <v>1</v>
       </c>
       <c r="B11" s="2">
-        <v>45616</v>
+        <v>45622</v>
       </c>
       <c r="C11" s="2">
-        <v>3</v>
+        <v>131</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -571,13 +571,13 @@
         <v>1</v>
       </c>
       <c r="B12" s="2">
-        <v>45617</v>
+        <v>45623</v>
       </c>
       <c r="C12" s="2">
-        <v>12</v>
+        <v>61</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -585,13 +585,13 @@
         <v>1</v>
       </c>
       <c r="B13" s="2">
-        <v>45618</v>
+        <v>45625</v>
       </c>
       <c r="C13" s="2">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -599,13 +599,13 @@
         <v>1</v>
       </c>
       <c r="B14" s="2">
-        <v>45619</v>
+        <v>45625</v>
       </c>
       <c r="C14" s="2">
-        <v>49</v>
+        <v>162</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -613,13 +613,13 @@
         <v>1</v>
       </c>
       <c r="B15" s="2">
-        <v>45621</v>
+        <v>45625</v>
       </c>
       <c r="C15" s="2">
-        <v>158</v>
+        <v>4</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -627,13 +627,13 @@
         <v>1</v>
       </c>
       <c r="B16" s="2">
-        <v>45622</v>
+        <v>45626</v>
       </c>
       <c r="C16" s="2">
-        <v>26</v>
+        <v>302</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -641,10 +641,10 @@
         <v>1</v>
       </c>
       <c r="B17" s="2">
-        <v>45622</v>
+        <v>45627</v>
       </c>
       <c r="C17" s="2">
-        <v>415</v>
+        <v>61</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>5</v>
@@ -655,10 +655,10 @@
         <v>1</v>
       </c>
       <c r="B18" s="2">
-        <v>45623</v>
+        <v>45628</v>
       </c>
       <c r="C18" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>5</v>
@@ -669,13 +669,13 @@
         <v>1</v>
       </c>
       <c r="B19" s="2">
-        <v>45623</v>
+        <v>45628</v>
       </c>
       <c r="C19" s="2">
-        <v>1</v>
+        <v>476</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -683,13 +683,13 @@
         <v>1</v>
       </c>
       <c r="B20" s="2">
-        <v>45624</v>
+        <v>45629</v>
       </c>
       <c r="C20" s="2">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -697,13 +697,13 @@
         <v>1</v>
       </c>
       <c r="B21" s="2">
-        <v>45624</v>
+        <v>45630</v>
       </c>
       <c r="C21" s="2">
-        <v>326</v>
+        <v>51</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -711,10 +711,10 @@
         <v>1</v>
       </c>
       <c r="B22" s="2">
-        <v>45625</v>
+        <v>45630</v>
       </c>
       <c r="C22" s="2">
-        <v>1</v>
+        <v>416</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>5</v>
@@ -725,13 +725,13 @@
         <v>1</v>
       </c>
       <c r="B23" s="2">
-        <v>45625</v>
+        <v>45631</v>
       </c>
       <c r="C23" s="2">
-        <v>25</v>
+        <v>383</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -739,10 +739,10 @@
         <v>1</v>
       </c>
       <c r="B24" s="2">
-        <v>45625</v>
+        <v>45632</v>
       </c>
       <c r="C24" s="2">
-        <v>935</v>
+        <v>7</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>5</v>
@@ -753,13 +753,13 @@
         <v>1</v>
       </c>
       <c r="B25" s="2">
-        <v>45627</v>
+        <v>45632</v>
       </c>
       <c r="C25" s="2">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -767,10 +767,10 @@
         <v>1</v>
       </c>
       <c r="B26" s="2">
-        <v>45628</v>
+        <v>45633</v>
       </c>
       <c r="C26" s="2">
-        <v>388</v>
+        <v>67</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>5</v>
@@ -781,10 +781,10 @@
         <v>1</v>
       </c>
       <c r="B27" s="2">
-        <v>45630</v>
+        <v>45633</v>
       </c>
       <c r="C27" s="2">
-        <v>5</v>
+        <v>881</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>5</v>
@@ -795,10 +795,10 @@
         <v>1</v>
       </c>
       <c r="B28" s="2">
-        <v>45631</v>
+        <v>45634</v>
       </c>
       <c r="C28" s="2">
-        <v>376</v>
+        <v>2</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>5</v>
@@ -809,13 +809,13 @@
         <v>1</v>
       </c>
       <c r="B29" s="2">
-        <v>45633</v>
+        <v>45634</v>
       </c>
       <c r="C29" s="2">
-        <v>15</v>
+        <v>945</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -823,13 +823,13 @@
         <v>1</v>
       </c>
       <c r="B30" s="2">
-        <v>45636</v>
+        <v>45635</v>
       </c>
       <c r="C30" s="2">
-        <v>642</v>
+        <v>5</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -837,13 +837,13 @@
         <v>1</v>
       </c>
       <c r="B31" s="2">
-        <v>45637</v>
+        <v>45636</v>
       </c>
       <c r="C31" s="2">
-        <v>32</v>
+        <v>338</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -851,10 +851,10 @@
         <v>1</v>
       </c>
       <c r="B32" s="2">
-        <v>45639</v>
+        <v>45638</v>
       </c>
       <c r="C32" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>5</v>
@@ -868,10 +868,10 @@
         <v>45639</v>
       </c>
       <c r="C33" s="2">
-        <v>807</v>
+        <v>816</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -882,10 +882,10 @@
         <v>45640</v>
       </c>
       <c r="C34" s="2">
-        <v>192</v>
+        <v>1</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -893,10 +893,10 @@
         <v>1</v>
       </c>
       <c r="B35" s="2">
-        <v>45642</v>
+        <v>45640</v>
       </c>
       <c r="C35" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>5</v>
@@ -907,13 +907,13 @@
         <v>1</v>
       </c>
       <c r="B36" s="2">
-        <v>45642</v>
+        <v>45641</v>
       </c>
       <c r="C36" s="2">
-        <v>1096</v>
+        <v>13</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -921,7 +921,7 @@
         <v>1</v>
       </c>
       <c r="B37" s="2">
-        <v>45643</v>
+        <v>45641</v>
       </c>
       <c r="C37" s="2">
         <v>1</v>
@@ -935,10 +935,10 @@
         <v>1</v>
       </c>
       <c r="B38" s="2">
-        <v>45643</v>
+        <v>45645</v>
       </c>
       <c r="C38" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>7</v>
@@ -949,10 +949,10 @@
         <v>1</v>
       </c>
       <c r="B39" s="2">
-        <v>45645</v>
+        <v>45647</v>
       </c>
       <c r="C39" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>5</v>
@@ -963,10 +963,10 @@
         <v>1</v>
       </c>
       <c r="B40" s="2">
-        <v>45646</v>
+        <v>45647</v>
       </c>
       <c r="C40" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>5</v>
@@ -977,10 +977,10 @@
         <v>1</v>
       </c>
       <c r="B41" s="2">
-        <v>45646</v>
+        <v>45648</v>
       </c>
       <c r="C41" s="2">
-        <v>179</v>
+        <v>279</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>7</v>
@@ -991,13 +991,13 @@
         <v>1</v>
       </c>
       <c r="B42" s="2">
-        <v>45647</v>
+        <v>45650</v>
       </c>
       <c r="C42" s="2">
-        <v>154</v>
+        <v>5</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1005,7 +1005,7 @@
         <v>1</v>
       </c>
       <c r="B43" s="2">
-        <v>45648</v>
+        <v>45651</v>
       </c>
       <c r="C43" s="2">
         <v>4</v>
@@ -1019,13 +1019,13 @@
         <v>1</v>
       </c>
       <c r="B44" s="2">
-        <v>45648</v>
+        <v>45651</v>
       </c>
       <c r="C44" s="2">
-        <v>70</v>
+        <v>288</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="B45" s="2">
-        <v>45649</v>
+        <v>45653</v>
       </c>
       <c r="C45" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>5</v>
@@ -1047,13 +1047,13 @@
         <v>1</v>
       </c>
       <c r="B46" s="2">
-        <v>45650</v>
+        <v>45654</v>
       </c>
       <c r="C46" s="2">
-        <v>283</v>
+        <v>455</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1061,13 +1061,13 @@
         <v>1</v>
       </c>
       <c r="B47" s="2">
-        <v>45651</v>
+        <v>45655</v>
       </c>
       <c r="C47" s="2">
-        <v>50</v>
+        <v>333</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1075,10 +1075,10 @@
         <v>1</v>
       </c>
       <c r="B48" s="2">
-        <v>45652</v>
+        <v>45656</v>
       </c>
       <c r="C48" s="2">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>5</v>
@@ -1089,7 +1089,7 @@
         <v>1</v>
       </c>
       <c r="B49" s="2">
-        <v>45652</v>
+        <v>45597</v>
       </c>
       <c r="C49" s="2">
         <v>1</v>
@@ -1103,13 +1103,13 @@
         <v>1</v>
       </c>
       <c r="B50" s="2">
-        <v>45653</v>
+        <v>45604</v>
       </c>
       <c r="C50" s="2">
         <v>18</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1117,10 +1117,10 @@
         <v>1</v>
       </c>
       <c r="B51" s="2">
-        <v>45654</v>
+        <v>45606</v>
       </c>
       <c r="C51" s="2">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>5</v>
@@ -1131,10 +1131,10 @@
         <v>1</v>
       </c>
       <c r="B52" s="2">
-        <v>45654</v>
+        <v>45606</v>
       </c>
       <c r="C52" s="2">
-        <v>663</v>
+        <v>549</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>5</v>
@@ -1145,13 +1145,13 @@
         <v>1</v>
       </c>
       <c r="B53" s="2">
-        <v>45655</v>
+        <v>45606</v>
       </c>
       <c r="C53" s="2">
-        <v>4</v>
+        <v>290</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1159,13 +1159,13 @@
         <v>1</v>
       </c>
       <c r="B54" s="2">
-        <v>45656</v>
+        <v>45607</v>
       </c>
       <c r="C54" s="2">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1173,13 +1173,13 @@
         <v>1</v>
       </c>
       <c r="B55" s="2">
-        <v>45656</v>
+        <v>45609</v>
       </c>
       <c r="C55" s="2">
-        <v>272</v>
+        <v>186</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1187,13 +1187,13 @@
         <v>1</v>
       </c>
       <c r="B56" s="2">
-        <v>45605</v>
+        <v>45610</v>
       </c>
       <c r="C56" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1201,13 +1201,13 @@
         <v>1</v>
       </c>
       <c r="B57" s="2">
-        <v>45605</v>
+        <v>45612</v>
       </c>
       <c r="C57" s="2">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1215,10 +1215,10 @@
         <v>1</v>
       </c>
       <c r="B58" s="2">
-        <v>45607</v>
+        <v>45613</v>
       </c>
       <c r="C58" s="2">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>5</v>
@@ -1229,13 +1229,13 @@
         <v>1</v>
       </c>
       <c r="B59" s="2">
-        <v>45608</v>
+        <v>45613</v>
       </c>
       <c r="C59" s="2">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1243,13 +1243,13 @@
         <v>1</v>
       </c>
       <c r="B60" s="2">
-        <v>45608</v>
+        <v>45615</v>
       </c>
       <c r="C60" s="2">
-        <v>155</v>
+        <v>3</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1257,10 +1257,10 @@
         <v>1</v>
       </c>
       <c r="B61" s="2">
-        <v>45610</v>
+        <v>45615</v>
       </c>
       <c r="C61" s="2">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>5</v>
@@ -1271,13 +1271,13 @@
         <v>1</v>
       </c>
       <c r="B62" s="2">
-        <v>45611</v>
+        <v>45618</v>
       </c>
       <c r="C62" s="2">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -1285,7 +1285,7 @@
         <v>1</v>
       </c>
       <c r="B63" s="2">
-        <v>45612</v>
+        <v>45619</v>
       </c>
       <c r="C63" s="2">
         <v>4</v>
@@ -1299,13 +1299,13 @@
         <v>1</v>
       </c>
       <c r="B64" s="2">
-        <v>45613</v>
+        <v>45619</v>
       </c>
       <c r="C64" s="2">
-        <v>32</v>
+        <v>163</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1313,10 +1313,10 @@
         <v>1</v>
       </c>
       <c r="B65" s="2">
-        <v>45614</v>
+        <v>45620</v>
       </c>
       <c r="C65" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>5</v>
@@ -1327,13 +1327,13 @@
         <v>1</v>
       </c>
       <c r="B66" s="2">
-        <v>45614</v>
+        <v>45621</v>
       </c>
       <c r="C66" s="2">
-        <v>236</v>
+        <v>33</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -1341,10 +1341,10 @@
         <v>1</v>
       </c>
       <c r="B67" s="2">
-        <v>45614</v>
+        <v>45622</v>
       </c>
       <c r="C67" s="2">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>8</v>
@@ -1355,10 +1355,10 @@
         <v>1</v>
       </c>
       <c r="B68" s="2">
-        <v>45616</v>
+        <v>45623</v>
       </c>
       <c r="C68" s="2">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>5</v>
@@ -1369,10 +1369,10 @@
         <v>1</v>
       </c>
       <c r="B69" s="2">
-        <v>45617</v>
+        <v>45624</v>
       </c>
       <c r="C69" s="2">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>5</v>
@@ -1383,13 +1383,13 @@
         <v>1</v>
       </c>
       <c r="B70" s="2">
-        <v>45617</v>
+        <v>45625</v>
       </c>
       <c r="C70" s="2">
-        <v>209</v>
+        <v>305</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -1397,13 +1397,13 @@
         <v>1</v>
       </c>
       <c r="B71" s="2">
-        <v>45617</v>
+        <v>45626</v>
       </c>
       <c r="C71" s="2">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1411,10 +1411,10 @@
         <v>1</v>
       </c>
       <c r="B72" s="2">
-        <v>45618</v>
+        <v>45626</v>
       </c>
       <c r="C72" s="2">
-        <v>8</v>
+        <v>757</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>5</v>
@@ -1425,13 +1425,13 @@
         <v>1</v>
       </c>
       <c r="B73" s="2">
-        <v>45618</v>
+        <v>45628</v>
       </c>
       <c r="C73" s="2">
-        <v>770</v>
+        <v>70</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -1439,13 +1439,13 @@
         <v>1</v>
       </c>
       <c r="B74" s="2">
-        <v>45620</v>
+        <v>45629</v>
       </c>
       <c r="C74" s="2">
-        <v>298</v>
+        <v>1</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -1453,10 +1453,10 @@
         <v>1</v>
       </c>
       <c r="B75" s="2">
-        <v>45621</v>
+        <v>45629</v>
       </c>
       <c r="C75" s="2">
-        <v>9</v>
+        <v>384</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>5</v>
@@ -1467,10 +1467,10 @@
         <v>1</v>
       </c>
       <c r="B76" s="2">
-        <v>45621</v>
+        <v>45632</v>
       </c>
       <c r="C76" s="2">
-        <v>480</v>
+        <v>893</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>5</v>
@@ -1481,13 +1481,13 @@
         <v>1</v>
       </c>
       <c r="B77" s="2">
-        <v>45623</v>
+        <v>45632</v>
       </c>
       <c r="C77" s="2">
-        <v>1</v>
+        <v>711</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -1495,13 +1495,13 @@
         <v>1</v>
       </c>
       <c r="B78" s="2">
-        <v>45624</v>
+        <v>45633</v>
       </c>
       <c r="C78" s="2">
-        <v>583</v>
+        <v>152</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -1509,10 +1509,10 @@
         <v>1</v>
       </c>
       <c r="B79" s="2">
-        <v>45627</v>
+        <v>45635</v>
       </c>
       <c r="C79" s="2">
-        <v>637</v>
+        <v>504</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>5</v>
@@ -1523,13 +1523,13 @@
         <v>1</v>
       </c>
       <c r="B80" s="2">
-        <v>45628</v>
+        <v>45635</v>
       </c>
       <c r="C80" s="2">
-        <v>53</v>
+        <v>735</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -1537,10 +1537,10 @@
         <v>1</v>
       </c>
       <c r="B81" s="2">
-        <v>45631</v>
+        <v>45636</v>
       </c>
       <c r="C81" s="2">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>7</v>
@@ -1551,13 +1551,13 @@
         <v>1</v>
       </c>
       <c r="B82" s="2">
-        <v>45634</v>
+        <v>45638</v>
       </c>
       <c r="C82" s="2">
-        <v>2</v>
+        <v>714</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -1565,10 +1565,10 @@
         <v>1</v>
       </c>
       <c r="B83" s="2">
-        <v>45634</v>
+        <v>45639</v>
       </c>
       <c r="C83" s="2">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>7</v>
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="B84" s="2">
-        <v>45636</v>
+        <v>45641</v>
       </c>
       <c r="C84" s="2">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>5</v>
@@ -1593,13 +1593,13 @@
         <v>1</v>
       </c>
       <c r="B85" s="2">
-        <v>45637</v>
+        <v>45642</v>
       </c>
       <c r="C85" s="2">
-        <v>1</v>
+        <v>83</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -1607,13 +1607,13 @@
         <v>1</v>
       </c>
       <c r="B86" s="2">
-        <v>45637</v>
+        <v>45644</v>
       </c>
       <c r="C86" s="2">
-        <v>778</v>
+        <v>4</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -1621,10 +1621,10 @@
         <v>1</v>
       </c>
       <c r="B87" s="2">
-        <v>45639</v>
+        <v>45644</v>
       </c>
       <c r="C87" s="2">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>5</v>
@@ -1635,7 +1635,7 @@
         <v>1</v>
       </c>
       <c r="B88" s="2">
-        <v>45640</v>
+        <v>45645</v>
       </c>
       <c r="C88" s="2">
         <v>1</v>
@@ -1649,10 +1649,10 @@
         <v>1</v>
       </c>
       <c r="B89" s="2">
-        <v>45640</v>
+        <v>45647</v>
       </c>
       <c r="C89" s="2">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>5</v>
@@ -1663,13 +1663,13 @@
         <v>1</v>
       </c>
       <c r="B90" s="2">
-        <v>45640</v>
+        <v>45648</v>
       </c>
       <c r="C90" s="2">
-        <v>1649</v>
+        <v>2</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -1677,10 +1677,10 @@
         <v>1</v>
       </c>
       <c r="B91" s="2">
-        <v>45642</v>
+        <v>45648</v>
       </c>
       <c r="C91" s="2">
-        <v>71</v>
+        <v>9</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>5</v>
@@ -1691,13 +1691,13 @@
         <v>1</v>
       </c>
       <c r="B92" s="2">
-        <v>45643</v>
+        <v>45650</v>
       </c>
       <c r="C92" s="2">
-        <v>1155</v>
+        <v>46</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -1705,10 +1705,10 @@
         <v>1</v>
       </c>
       <c r="B93" s="2">
-        <v>45643</v>
+        <v>45651</v>
       </c>
       <c r="C93" s="2">
-        <v>50</v>
+        <v>532</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>8</v>
@@ -1719,10 +1719,10 @@
         <v>1</v>
       </c>
       <c r="B94" s="2">
-        <v>45644</v>
+        <v>45652</v>
       </c>
       <c r="C94" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>5</v>
@@ -1733,10 +1733,10 @@
         <v>1</v>
       </c>
       <c r="B95" s="2">
-        <v>45645</v>
+        <v>45653</v>
       </c>
       <c r="C95" s="2">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>5</v>
@@ -1747,13 +1747,13 @@
         <v>1</v>
       </c>
       <c r="B96" s="2">
-        <v>45646</v>
+        <v>45654</v>
       </c>
       <c r="C96" s="2">
-        <v>3</v>
+        <v>239</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -1761,13 +1761,13 @@
         <v>1</v>
       </c>
       <c r="B97" s="2">
-        <v>45646</v>
+        <v>45655</v>
       </c>
       <c r="C97" s="2">
-        <v>936</v>
+        <v>5</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -1775,13 +1775,13 @@
         <v>1</v>
       </c>
       <c r="B98" s="2">
-        <v>45646</v>
+        <v>45604</v>
       </c>
       <c r="C98" s="2">
-        <v>117</v>
+        <v>2</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -1789,10 +1789,10 @@
         <v>1</v>
       </c>
       <c r="B99" s="2">
-        <v>45647</v>
+        <v>45605</v>
       </c>
       <c r="C99" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>5</v>
@@ -1803,10 +1803,10 @@
         <v>1</v>
       </c>
       <c r="B100" s="2">
-        <v>45649</v>
+        <v>45605</v>
       </c>
       <c r="C100" s="2">
-        <v>3</v>
+        <v>512</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>5</v>
@@ -1817,13 +1817,13 @@
         <v>1</v>
       </c>
       <c r="B101" s="2">
-        <v>45649</v>
+        <v>45607</v>
       </c>
       <c r="C101" s="2">
-        <v>138</v>
+        <v>1</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -1831,13 +1831,13 @@
         <v>1</v>
       </c>
       <c r="B102" s="2">
-        <v>45650</v>
+        <v>45607</v>
       </c>
       <c r="C102" s="2">
-        <v>16</v>
+        <v>103</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -1845,10 +1845,10 @@
         <v>1</v>
       </c>
       <c r="B103" s="2">
-        <v>45650</v>
+        <v>45608</v>
       </c>
       <c r="C103" s="2">
-        <v>766</v>
+        <v>235</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>5</v>
@@ -1859,10 +1859,10 @@
         <v>1</v>
       </c>
       <c r="B104" s="2">
-        <v>45652</v>
+        <v>45611</v>
       </c>
       <c r="C104" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>5</v>
@@ -1873,13 +1873,13 @@
         <v>1</v>
       </c>
       <c r="B105" s="2">
-        <v>45652</v>
+        <v>45612</v>
       </c>
       <c r="C105" s="2">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -1887,13 +1887,13 @@
         <v>1</v>
       </c>
       <c r="B106" s="2">
-        <v>45653</v>
+        <v>45615</v>
       </c>
       <c r="C106" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -1901,13 +1901,13 @@
         <v>1</v>
       </c>
       <c r="B107" s="2">
-        <v>45653</v>
+        <v>45618</v>
       </c>
       <c r="C107" s="2">
-        <v>533</v>
+        <v>44</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -1915,10 +1915,10 @@
         <v>1</v>
       </c>
       <c r="B108" s="2">
-        <v>45656</v>
+        <v>45621</v>
       </c>
       <c r="C108" s="2">
-        <v>633</v>
+        <v>2</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>5</v>
@@ -1929,13 +1929,13 @@
         <v>1</v>
       </c>
       <c r="B109" s="2">
-        <v>45604</v>
+        <v>45621</v>
       </c>
       <c r="C109" s="2">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -1943,10 +1943,10 @@
         <v>1</v>
       </c>
       <c r="B110" s="2">
-        <v>45604</v>
+        <v>45623</v>
       </c>
       <c r="C110" s="2">
-        <v>789</v>
+        <v>28</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>5</v>
@@ -1957,13 +1957,13 @@
         <v>1</v>
       </c>
       <c r="B111" s="2">
-        <v>45605</v>
+        <v>45624</v>
       </c>
       <c r="C111" s="2">
-        <v>237</v>
+        <v>2</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -1971,13 +1971,13 @@
         <v>1</v>
       </c>
       <c r="B112" s="2">
-        <v>45606</v>
+        <v>45624</v>
       </c>
       <c r="C112" s="2">
-        <v>4</v>
+        <v>824</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -1985,10 +1985,10 @@
         <v>1</v>
       </c>
       <c r="B113" s="2">
-        <v>45607</v>
+        <v>45626</v>
       </c>
       <c r="C113" s="2">
-        <v>904</v>
+        <v>39</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>5</v>
@@ -1999,10 +1999,10 @@
         <v>1</v>
       </c>
       <c r="B114" s="2">
-        <v>45609</v>
+        <v>45626</v>
       </c>
       <c r="C114" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>5</v>
@@ -2013,13 +2013,13 @@
         <v>1</v>
       </c>
       <c r="B115" s="2">
-        <v>45616</v>
+        <v>45627</v>
       </c>
       <c r="C115" s="2">
-        <v>4</v>
+        <v>786</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2027,13 +2027,13 @@
         <v>1</v>
       </c>
       <c r="B116" s="2">
-        <v>45619</v>
+        <v>45627</v>
       </c>
       <c r="C116" s="2">
-        <v>77</v>
+        <v>160</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2041,7 +2041,7 @@
         <v>1</v>
       </c>
       <c r="B117" s="2">
-        <v>45622</v>
+        <v>45628</v>
       </c>
       <c r="C117" s="2">
         <v>1</v>
@@ -2055,13 +2055,13 @@
         <v>1</v>
       </c>
       <c r="B118" s="2">
-        <v>45622</v>
+        <v>45629</v>
       </c>
       <c r="C118" s="2">
-        <v>131</v>
+        <v>40</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -2069,13 +2069,13 @@
         <v>1</v>
       </c>
       <c r="B119" s="2">
-        <v>45623</v>
+        <v>45630</v>
       </c>
       <c r="C119" s="2">
-        <v>61</v>
+        <v>485</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2083,13 +2083,13 @@
         <v>1</v>
       </c>
       <c r="B120" s="2">
-        <v>45625</v>
+        <v>45630</v>
       </c>
       <c r="C120" s="2">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -2097,13 +2097,13 @@
         <v>1</v>
       </c>
       <c r="B121" s="2">
-        <v>45625</v>
+        <v>45631</v>
       </c>
       <c r="C121" s="2">
-        <v>162</v>
+        <v>4</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2111,10 +2111,10 @@
         <v>1</v>
       </c>
       <c r="B122" s="2">
-        <v>45625</v>
+        <v>45633</v>
       </c>
       <c r="C122" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>5</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="B123" s="2">
-        <v>45626</v>
+        <v>45633</v>
       </c>
       <c r="C123" s="2">
-        <v>302</v>
+        <v>1404</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -2139,13 +2139,13 @@
         <v>1</v>
       </c>
       <c r="B124" s="2">
-        <v>45627</v>
+        <v>45633</v>
       </c>
       <c r="C124" s="2">
-        <v>61</v>
+        <v>118</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -2153,10 +2153,10 @@
         <v>1</v>
       </c>
       <c r="B125" s="2">
-        <v>45628</v>
+        <v>45634</v>
       </c>
       <c r="C125" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>5</v>
@@ -2167,13 +2167,13 @@
         <v>1</v>
       </c>
       <c r="B126" s="2">
-        <v>45628</v>
+        <v>45634</v>
       </c>
       <c r="C126" s="2">
-        <v>476</v>
+        <v>854</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -2181,13 +2181,13 @@
         <v>1</v>
       </c>
       <c r="B127" s="2">
-        <v>45629</v>
+        <v>45636</v>
       </c>
       <c r="C127" s="2">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -2195,13 +2195,13 @@
         <v>1</v>
       </c>
       <c r="B128" s="2">
-        <v>45630</v>
+        <v>45636</v>
       </c>
       <c r="C128" s="2">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -2209,10 +2209,10 @@
         <v>1</v>
       </c>
       <c r="B129" s="2">
-        <v>45630</v>
+        <v>45637</v>
       </c>
       <c r="C129" s="2">
-        <v>416</v>
+        <v>2</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>5</v>
@@ -2223,13 +2223,13 @@
         <v>1</v>
       </c>
       <c r="B130" s="2">
-        <v>45631</v>
+        <v>45637</v>
       </c>
       <c r="C130" s="2">
-        <v>383</v>
+        <v>535</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -2237,10 +2237,10 @@
         <v>1</v>
       </c>
       <c r="B131" s="2">
-        <v>45632</v>
+        <v>45640</v>
       </c>
       <c r="C131" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>5</v>
@@ -2251,13 +2251,13 @@
         <v>1</v>
       </c>
       <c r="B132" s="2">
-        <v>45632</v>
+        <v>45640</v>
       </c>
       <c r="C132" s="2">
-        <v>50</v>
+        <v>829</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -2265,10 +2265,10 @@
         <v>1</v>
       </c>
       <c r="B133" s="2">
-        <v>45633</v>
+        <v>45641</v>
       </c>
       <c r="C133" s="2">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>5</v>
@@ -2279,13 +2279,13 @@
         <v>1</v>
       </c>
       <c r="B134" s="2">
-        <v>45633</v>
+        <v>45641</v>
       </c>
       <c r="C134" s="2">
-        <v>881</v>
+        <v>155</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -2293,10 +2293,10 @@
         <v>1</v>
       </c>
       <c r="B135" s="2">
-        <v>45634</v>
+        <v>45643</v>
       </c>
       <c r="C135" s="2">
-        <v>2</v>
+        <v>523</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>5</v>
@@ -2307,13 +2307,13 @@
         <v>1</v>
       </c>
       <c r="B136" s="2">
-        <v>45634</v>
+        <v>45644</v>
       </c>
       <c r="C136" s="2">
-        <v>945</v>
+        <v>85</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -2321,10 +2321,10 @@
         <v>1</v>
       </c>
       <c r="B137" s="2">
-        <v>45635</v>
+        <v>45647</v>
       </c>
       <c r="C137" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>5</v>
@@ -2335,10 +2335,10 @@
         <v>1</v>
       </c>
       <c r="B138" s="2">
-        <v>45636</v>
+        <v>45647</v>
       </c>
       <c r="C138" s="2">
-        <v>338</v>
+        <v>1</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>5</v>
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B139" s="2">
-        <v>45638</v>
+        <v>45647</v>
       </c>
       <c r="C139" s="2">
-        <v>2</v>
+        <v>254</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -2363,10 +2363,10 @@
         <v>1</v>
       </c>
       <c r="B140" s="2">
-        <v>45639</v>
+        <v>45648</v>
       </c>
       <c r="C140" s="2">
-        <v>816</v>
+        <v>5</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>5</v>
@@ -2377,10 +2377,10 @@
         <v>1</v>
       </c>
       <c r="B141" s="2">
-        <v>45640</v>
+        <v>45650</v>
       </c>
       <c r="C141" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>5</v>
@@ -2391,10 +2391,10 @@
         <v>1</v>
       </c>
       <c r="B142" s="2">
-        <v>45640</v>
+        <v>45650</v>
       </c>
       <c r="C142" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>5</v>
@@ -2405,13 +2405,13 @@
         <v>1</v>
       </c>
       <c r="B143" s="2">
-        <v>45641</v>
+        <v>45650</v>
       </c>
       <c r="C143" s="2">
-        <v>13</v>
+        <v>316</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -2419,10 +2419,10 @@
         <v>1</v>
       </c>
       <c r="B144" s="2">
-        <v>45641</v>
+        <v>45652</v>
       </c>
       <c r="C144" s="2">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>5</v>
@@ -2433,13 +2433,13 @@
         <v>1</v>
       </c>
       <c r="B145" s="2">
-        <v>45645</v>
+        <v>45653</v>
       </c>
       <c r="C145" s="2">
-        <v>147</v>
+        <v>1776</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -2447,10 +2447,10 @@
         <v>1</v>
       </c>
       <c r="B146" s="2">
-        <v>45647</v>
+        <v>45655</v>
       </c>
       <c r="C146" s="2">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>5</v>
@@ -2461,13 +2461,13 @@
         <v>1</v>
       </c>
       <c r="B147" s="2">
-        <v>45647</v>
+        <v>45656</v>
       </c>
       <c r="C147" s="2">
-        <v>5</v>
+        <v>1705</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -2475,13 +2475,13 @@
         <v>1</v>
       </c>
       <c r="B148" s="2">
-        <v>45648</v>
+        <v>45605</v>
       </c>
       <c r="C148" s="2">
-        <v>279</v>
+        <v>17</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -2489,13 +2489,13 @@
         <v>1</v>
       </c>
       <c r="B149" s="2">
-        <v>45650</v>
+        <v>45606</v>
       </c>
       <c r="C149" s="2">
-        <v>5</v>
+        <v>211</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -2503,10 +2503,10 @@
         <v>1</v>
       </c>
       <c r="B150" s="2">
-        <v>45651</v>
+        <v>45607</v>
       </c>
       <c r="C150" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>5</v>
@@ -2517,13 +2517,13 @@
         <v>1</v>
       </c>
       <c r="B151" s="2">
-        <v>45651</v>
+        <v>45608</v>
       </c>
       <c r="C151" s="2">
-        <v>288</v>
+        <v>16</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -2531,13 +2531,13 @@
         <v>1</v>
       </c>
       <c r="B152" s="2">
-        <v>45653</v>
+        <v>45609</v>
       </c>
       <c r="C152" s="2">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -2545,13 +2545,13 @@
         <v>1</v>
       </c>
       <c r="B153" s="2">
-        <v>45654</v>
+        <v>45610</v>
       </c>
       <c r="C153" s="2">
-        <v>455</v>
+        <v>1</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -2559,13 +2559,13 @@
         <v>1</v>
       </c>
       <c r="B154" s="2">
-        <v>45655</v>
+        <v>45610</v>
       </c>
       <c r="C154" s="2">
-        <v>333</v>
+        <v>237</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -2573,13 +2573,13 @@
         <v>1</v>
       </c>
       <c r="B155" s="2">
-        <v>45656</v>
+        <v>45612</v>
       </c>
       <c r="C155" s="2">
-        <v>48</v>
+        <v>208</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -2587,10 +2587,10 @@
         <v>1</v>
       </c>
       <c r="B156" s="2">
-        <v>45604</v>
+        <v>45613</v>
       </c>
       <c r="C156" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>5</v>
@@ -2601,10 +2601,10 @@
         <v>1</v>
       </c>
       <c r="B157" s="2">
-        <v>45605</v>
+        <v>45613</v>
       </c>
       <c r="C157" s="2">
-        <v>2</v>
+        <v>606</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>5</v>
@@ -2615,13 +2615,13 @@
         <v>1</v>
       </c>
       <c r="B158" s="2">
-        <v>45605</v>
+        <v>45615</v>
       </c>
       <c r="C158" s="2">
-        <v>512</v>
+        <v>17</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -2629,10 +2629,10 @@
         <v>1</v>
       </c>
       <c r="B159" s="2">
-        <v>45607</v>
+        <v>45616</v>
       </c>
       <c r="C159" s="2">
-        <v>1</v>
+        <v>317</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>5</v>
@@ -2643,13 +2643,13 @@
         <v>1</v>
       </c>
       <c r="B160" s="2">
-        <v>45607</v>
+        <v>45616</v>
       </c>
       <c r="C160" s="2">
-        <v>103</v>
+        <v>202</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -2657,10 +2657,10 @@
         <v>1</v>
       </c>
       <c r="B161" s="2">
-        <v>45608</v>
+        <v>45619</v>
       </c>
       <c r="C161" s="2">
-        <v>235</v>
+        <v>779</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>5</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="B162" s="2">
-        <v>45611</v>
+        <v>45619</v>
       </c>
       <c r="C162" s="2">
+        <v>719</v>
+      </c>
+      <c r="D162" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="D162" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -2685,10 +2685,10 @@
         <v>1</v>
       </c>
       <c r="B163" s="2">
-        <v>45612</v>
+        <v>45620</v>
       </c>
       <c r="C163" s="2">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>7</v>
@@ -2699,13 +2699,13 @@
         <v>1</v>
       </c>
       <c r="B164" s="2">
-        <v>45615</v>
+        <v>45622</v>
       </c>
       <c r="C164" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -2713,13 +2713,13 @@
         <v>1</v>
       </c>
       <c r="B165" s="2">
-        <v>45618</v>
+        <v>45622</v>
       </c>
       <c r="C165" s="2">
-        <v>44</v>
+        <v>560</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -2727,10 +2727,10 @@
         <v>1</v>
       </c>
       <c r="B166" s="2">
-        <v>45621</v>
+        <v>45623</v>
       </c>
       <c r="C166" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>5</v>
@@ -2741,10 +2741,10 @@
         <v>1</v>
       </c>
       <c r="B167" s="2">
-        <v>45621</v>
+        <v>45623</v>
       </c>
       <c r="C167" s="2">
-        <v>77</v>
+        <v>126</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>7</v>
@@ -2755,10 +2755,10 @@
         <v>1</v>
       </c>
       <c r="B168" s="2">
-        <v>45623</v>
+        <v>45625</v>
       </c>
       <c r="C168" s="2">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>5</v>
@@ -2769,13 +2769,13 @@
         <v>1</v>
       </c>
       <c r="B169" s="2">
-        <v>45624</v>
+        <v>45625</v>
       </c>
       <c r="C169" s="2">
-        <v>2</v>
+        <v>1117</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -2783,13 +2783,13 @@
         <v>1</v>
       </c>
       <c r="B170" s="2">
-        <v>45624</v>
+        <v>45626</v>
       </c>
       <c r="C170" s="2">
-        <v>824</v>
+        <v>3</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -2800,10 +2800,10 @@
         <v>45626</v>
       </c>
       <c r="C171" s="2">
-        <v>39</v>
+        <v>128</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -2811,10 +2811,10 @@
         <v>1</v>
       </c>
       <c r="B172" s="2">
-        <v>45626</v>
+        <v>45628</v>
       </c>
       <c r="C172" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>5</v>
@@ -2825,13 +2825,13 @@
         <v>1</v>
       </c>
       <c r="B173" s="2">
-        <v>45627</v>
+        <v>45628</v>
       </c>
       <c r="C173" s="2">
-        <v>786</v>
+        <v>33</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -2839,13 +2839,13 @@
         <v>1</v>
       </c>
       <c r="B174" s="2">
-        <v>45627</v>
+        <v>45629</v>
       </c>
       <c r="C174" s="2">
-        <v>160</v>
+        <v>4</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -2853,10 +2853,10 @@
         <v>1</v>
       </c>
       <c r="B175" s="2">
-        <v>45628</v>
+        <v>45631</v>
       </c>
       <c r="C175" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>5</v>
@@ -2867,10 +2867,10 @@
         <v>1</v>
       </c>
       <c r="B176" s="2">
-        <v>45629</v>
+        <v>45631</v>
       </c>
       <c r="C176" s="2">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>5</v>
@@ -2881,13 +2881,13 @@
         <v>1</v>
       </c>
       <c r="B177" s="2">
-        <v>45630</v>
+        <v>45634</v>
       </c>
       <c r="C177" s="2">
-        <v>485</v>
+        <v>1</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -2895,13 +2895,13 @@
         <v>1</v>
       </c>
       <c r="B178" s="2">
-        <v>45630</v>
+        <v>45634</v>
       </c>
       <c r="C178" s="2">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -2909,13 +2909,13 @@
         <v>1</v>
       </c>
       <c r="B179" s="2">
-        <v>45631</v>
+        <v>45635</v>
       </c>
       <c r="C179" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -2923,10 +2923,10 @@
         <v>1</v>
       </c>
       <c r="B180" s="2">
-        <v>45633</v>
+        <v>45636</v>
       </c>
       <c r="C180" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>5</v>
@@ -2937,13 +2937,13 @@
         <v>1</v>
       </c>
       <c r="B181" s="2">
-        <v>45633</v>
+        <v>45637</v>
       </c>
       <c r="C181" s="2">
-        <v>1404</v>
+        <v>64</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -2951,10 +2951,10 @@
         <v>1</v>
       </c>
       <c r="B182" s="2">
-        <v>45633</v>
+        <v>45638</v>
       </c>
       <c r="C182" s="2">
-        <v>118</v>
+        <v>29</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>8</v>
@@ -2965,10 +2965,10 @@
         <v>1</v>
       </c>
       <c r="B183" s="2">
-        <v>45634</v>
+        <v>45639</v>
       </c>
       <c r="C183" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>5</v>
@@ -2979,13 +2979,13 @@
         <v>1</v>
       </c>
       <c r="B184" s="2">
-        <v>45634</v>
+        <v>45641</v>
       </c>
       <c r="C184" s="2">
-        <v>854</v>
+        <v>98</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -2993,10 +2993,10 @@
         <v>1</v>
       </c>
       <c r="B185" s="2">
-        <v>45636</v>
+        <v>45642</v>
       </c>
       <c r="C185" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>5</v>
@@ -3007,13 +3007,13 @@
         <v>1</v>
       </c>
       <c r="B186" s="2">
-        <v>45636</v>
+        <v>45642</v>
       </c>
       <c r="C186" s="2">
-        <v>0</v>
+        <v>602</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -3021,13 +3021,13 @@
         <v>1</v>
       </c>
       <c r="B187" s="2">
-        <v>45637</v>
+        <v>45644</v>
       </c>
       <c r="C187" s="2">
-        <v>2</v>
+        <v>75</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -3035,10 +3035,10 @@
         <v>1</v>
       </c>
       <c r="B188" s="2">
-        <v>45637</v>
+        <v>45645</v>
       </c>
       <c r="C188" s="2">
-        <v>535</v>
+        <v>2</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>5</v>
@@ -3049,10 +3049,10 @@
         <v>1</v>
       </c>
       <c r="B189" s="2">
-        <v>45640</v>
+        <v>45645</v>
       </c>
       <c r="C189" s="2">
-        <v>1</v>
+        <v>607</v>
       </c>
       <c r="D189" s="2" t="s">
         <v>5</v>
@@ -3063,13 +3063,13 @@
         <v>1</v>
       </c>
       <c r="B190" s="2">
-        <v>45640</v>
+        <v>45645</v>
       </c>
       <c r="C190" s="2">
-        <v>829</v>
+        <v>1230</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -3077,10 +3077,10 @@
         <v>1</v>
       </c>
       <c r="B191" s="2">
-        <v>45641</v>
+        <v>45648</v>
       </c>
       <c r="C191" s="2">
-        <v>2</v>
+        <v>903</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>5</v>
@@ -3091,13 +3091,13 @@
         <v>1</v>
       </c>
       <c r="B192" s="2">
-        <v>45641</v>
+        <v>45648</v>
       </c>
       <c r="C192" s="2">
-        <v>155</v>
+        <v>1613</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -3105,13 +3105,13 @@
         <v>1</v>
       </c>
       <c r="B193" s="2">
-        <v>45643</v>
+        <v>45649</v>
       </c>
       <c r="C193" s="2">
-        <v>523</v>
+        <v>241</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -3119,13 +3119,13 @@
         <v>1</v>
       </c>
       <c r="B194" s="2">
-        <v>45644</v>
+        <v>45650</v>
       </c>
       <c r="C194" s="2">
-        <v>85</v>
+        <v>1</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -3133,10 +3133,10 @@
         <v>1</v>
       </c>
       <c r="B195" s="2">
-        <v>45647</v>
+        <v>45651</v>
       </c>
       <c r="C195" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D195" s="2" t="s">
         <v>5</v>
@@ -3147,10 +3147,10 @@
         <v>1</v>
       </c>
       <c r="B196" s="2">
-        <v>45647</v>
+        <v>45651</v>
       </c>
       <c r="C196" s="2">
-        <v>1</v>
+        <v>830</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>5</v>
@@ -3161,13 +3161,13 @@
         <v>1</v>
       </c>
       <c r="B197" s="2">
-        <v>45647</v>
+        <v>45651</v>
       </c>
       <c r="C197" s="2">
-        <v>254</v>
+        <v>1321</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -3175,13 +3175,13 @@
         <v>1</v>
       </c>
       <c r="B198" s="2">
-        <v>45648</v>
+        <v>45652</v>
       </c>
       <c r="C198" s="2">
-        <v>5</v>
+        <v>384</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -3189,10 +3189,10 @@
         <v>1</v>
       </c>
       <c r="B199" s="2">
-        <v>45650</v>
+        <v>45654</v>
       </c>
       <c r="C199" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D199" s="2" t="s">
         <v>5</v>
@@ -3203,13 +3203,13 @@
         <v>1</v>
       </c>
       <c r="B200" s="2">
-        <v>45650</v>
+        <v>45654</v>
       </c>
       <c r="C200" s="2">
+        <v>1825</v>
+      </c>
+      <c r="D200" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="D200" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -3217,13 +3217,13 @@
         <v>1</v>
       </c>
       <c r="B201" s="2">
-        <v>45650</v>
+        <v>45655</v>
       </c>
       <c r="C201" s="2">
-        <v>316</v>
+        <v>1</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -3231,13 +3231,13 @@
         <v>1</v>
       </c>
       <c r="B202" s="2">
-        <v>45652</v>
+        <v>45655</v>
       </c>
       <c r="C202" s="2">
-        <v>31</v>
+        <v>493</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -3245,13 +3245,13 @@
         <v>1</v>
       </c>
       <c r="B203" s="2">
-        <v>45653</v>
+        <v>45604</v>
       </c>
       <c r="C203" s="2">
-        <v>1776</v>
+        <v>13</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -3259,10 +3259,10 @@
         <v>1</v>
       </c>
       <c r="B204" s="2">
-        <v>45655</v>
+        <v>45604</v>
       </c>
       <c r="C204" s="2">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>5</v>
@@ -3273,10 +3273,10 @@
         <v>1</v>
       </c>
       <c r="B205" s="2">
-        <v>45656</v>
+        <v>45604</v>
       </c>
       <c r="C205" s="2">
-        <v>1705</v>
+        <v>139</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>6</v>
@@ -3287,13 +3287,13 @@
         <v>1</v>
       </c>
       <c r="B206" s="2">
-        <v>45597</v>
+        <v>45607</v>
       </c>
       <c r="C206" s="2">
-        <v>1</v>
+        <v>473</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -3301,10 +3301,10 @@
         <v>1</v>
       </c>
       <c r="B207" s="2">
-        <v>45604</v>
+        <v>45608</v>
       </c>
       <c r="C207" s="2">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>7</v>
@@ -3315,13 +3315,13 @@
         <v>1</v>
       </c>
       <c r="B208" s="2">
-        <v>45606</v>
+        <v>45610</v>
       </c>
       <c r="C208" s="2">
-        <v>3</v>
+        <v>120</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -3329,13 +3329,13 @@
         <v>1</v>
       </c>
       <c r="B209" s="2">
-        <v>45606</v>
+        <v>45611</v>
       </c>
       <c r="C209" s="2">
-        <v>549</v>
+        <v>0</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -3343,10 +3343,10 @@
         <v>1</v>
       </c>
       <c r="B210" s="2">
-        <v>45606</v>
+        <v>45613</v>
       </c>
       <c r="C210" s="2">
-        <v>290</v>
+        <v>468</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>6</v>
@@ -3357,10 +3357,10 @@
         <v>1</v>
       </c>
       <c r="B211" s="2">
-        <v>45607</v>
+        <v>45614</v>
       </c>
       <c r="C211" s="2">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D211" s="2" t="s">
         <v>7</v>
@@ -3371,13 +3371,13 @@
         <v>1</v>
       </c>
       <c r="B212" s="2">
-        <v>45609</v>
+        <v>45616</v>
       </c>
       <c r="C212" s="2">
-        <v>186</v>
+        <v>3</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -3385,10 +3385,10 @@
         <v>1</v>
       </c>
       <c r="B213" s="2">
-        <v>45610</v>
+        <v>45617</v>
       </c>
       <c r="C213" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D213" s="2" t="s">
         <v>7</v>
@@ -3399,13 +3399,13 @@
         <v>1</v>
       </c>
       <c r="B214" s="2">
-        <v>45612</v>
+        <v>45618</v>
       </c>
       <c r="C214" s="2">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -3413,10 +3413,10 @@
         <v>1</v>
       </c>
       <c r="B215" s="2">
-        <v>45613</v>
+        <v>45619</v>
       </c>
       <c r="C215" s="2">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>5</v>
@@ -3427,13 +3427,13 @@
         <v>1</v>
       </c>
       <c r="B216" s="2">
-        <v>45613</v>
+        <v>45621</v>
       </c>
       <c r="C216" s="2">
-        <v>31</v>
+        <v>158</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -3441,10 +3441,10 @@
         <v>1</v>
       </c>
       <c r="B217" s="2">
-        <v>45615</v>
+        <v>45622</v>
       </c>
       <c r="C217" s="2">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>5</v>
@@ -3455,10 +3455,10 @@
         <v>1</v>
       </c>
       <c r="B218" s="2">
-        <v>45615</v>
+        <v>45622</v>
       </c>
       <c r="C218" s="2">
-        <v>24</v>
+        <v>415</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>5</v>
@@ -3469,10 +3469,10 @@
         <v>1</v>
       </c>
       <c r="B219" s="2">
-        <v>45618</v>
+        <v>45623</v>
       </c>
       <c r="C219" s="2">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>5</v>
@@ -3483,10 +3483,10 @@
         <v>1</v>
       </c>
       <c r="B220" s="2">
-        <v>45619</v>
+        <v>45623</v>
       </c>
       <c r="C220" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>5</v>
@@ -3497,13 +3497,13 @@
         <v>1</v>
       </c>
       <c r="B221" s="2">
-        <v>45619</v>
+        <v>45624</v>
       </c>
       <c r="C221" s="2">
-        <v>163</v>
+        <v>7</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -3511,13 +3511,13 @@
         <v>1</v>
       </c>
       <c r="B222" s="2">
-        <v>45620</v>
+        <v>45624</v>
       </c>
       <c r="C222" s="2">
-        <v>7</v>
+        <v>326</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -3525,10 +3525,10 @@
         <v>1</v>
       </c>
       <c r="B223" s="2">
-        <v>45621</v>
+        <v>45625</v>
       </c>
       <c r="C223" s="2">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>5</v>
@@ -3539,13 +3539,13 @@
         <v>1</v>
       </c>
       <c r="B224" s="2">
-        <v>45622</v>
+        <v>45625</v>
       </c>
       <c r="C224" s="2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -3553,10 +3553,10 @@
         <v>1</v>
       </c>
       <c r="B225" s="2">
-        <v>45623</v>
+        <v>45625</v>
       </c>
       <c r="C225" s="2">
-        <v>12</v>
+        <v>935</v>
       </c>
       <c r="D225" s="2" t="s">
         <v>5</v>
@@ -3567,10 +3567,10 @@
         <v>1</v>
       </c>
       <c r="B226" s="2">
-        <v>45624</v>
+        <v>45627</v>
       </c>
       <c r="C226" s="2">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="D226" s="2" t="s">
         <v>5</v>
@@ -3581,13 +3581,13 @@
         <v>1</v>
       </c>
       <c r="B227" s="2">
-        <v>45625</v>
+        <v>45628</v>
       </c>
       <c r="C227" s="2">
-        <v>305</v>
+        <v>388</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -3595,10 +3595,10 @@
         <v>1</v>
       </c>
       <c r="B228" s="2">
-        <v>45626</v>
+        <v>45630</v>
       </c>
       <c r="C228" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D228" s="2" t="s">
         <v>5</v>
@@ -3609,10 +3609,10 @@
         <v>1</v>
       </c>
       <c r="B229" s="2">
-        <v>45626</v>
+        <v>45631</v>
       </c>
       <c r="C229" s="2">
-        <v>757</v>
+        <v>376</v>
       </c>
       <c r="D229" s="2" t="s">
         <v>5</v>
@@ -3623,13 +3623,13 @@
         <v>1</v>
       </c>
       <c r="B230" s="2">
-        <v>45628</v>
+        <v>45633</v>
       </c>
       <c r="C230" s="2">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -3637,13 +3637,13 @@
         <v>1</v>
       </c>
       <c r="B231" s="2">
-        <v>45629</v>
+        <v>45636</v>
       </c>
       <c r="C231" s="2">
-        <v>1</v>
+        <v>642</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -3651,13 +3651,13 @@
         <v>1</v>
       </c>
       <c r="B232" s="2">
-        <v>45629</v>
+        <v>45637</v>
       </c>
       <c r="C232" s="2">
-        <v>384</v>
+        <v>32</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -3665,10 +3665,10 @@
         <v>1</v>
       </c>
       <c r="B233" s="2">
-        <v>45632</v>
+        <v>45639</v>
       </c>
       <c r="C233" s="2">
-        <v>893</v>
+        <v>1</v>
       </c>
       <c r="D233" s="2" t="s">
         <v>5</v>
@@ -3679,10 +3679,10 @@
         <v>1</v>
       </c>
       <c r="B234" s="2">
-        <v>45632</v>
+        <v>45639</v>
       </c>
       <c r="C234" s="2">
-        <v>711</v>
+        <v>807</v>
       </c>
       <c r="D234" s="2" t="s">
         <v>6</v>
@@ -3693,10 +3693,10 @@
         <v>1</v>
       </c>
       <c r="B235" s="2">
-        <v>45633</v>
+        <v>45640</v>
       </c>
       <c r="C235" s="2">
-        <v>152</v>
+        <v>192</v>
       </c>
       <c r="D235" s="2" t="s">
         <v>7</v>
@@ -3707,10 +3707,10 @@
         <v>1</v>
       </c>
       <c r="B236" s="2">
-        <v>45635</v>
+        <v>45642</v>
       </c>
       <c r="C236" s="2">
-        <v>504</v>
+        <v>1</v>
       </c>
       <c r="D236" s="2" t="s">
         <v>5</v>
@@ -3721,10 +3721,10 @@
         <v>1</v>
       </c>
       <c r="B237" s="2">
-        <v>45635</v>
+        <v>45642</v>
       </c>
       <c r="C237" s="2">
-        <v>735</v>
+        <v>1096</v>
       </c>
       <c r="D237" s="2" t="s">
         <v>6</v>
@@ -3735,13 +3735,13 @@
         <v>1</v>
       </c>
       <c r="B238" s="2">
-        <v>45636</v>
+        <v>45643</v>
       </c>
       <c r="C238" s="2">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -3749,13 +3749,13 @@
         <v>1</v>
       </c>
       <c r="B239" s="2">
-        <v>45638</v>
+        <v>45643</v>
       </c>
       <c r="C239" s="2">
-        <v>714</v>
+        <v>78</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -3763,13 +3763,13 @@
         <v>1</v>
       </c>
       <c r="B240" s="2">
-        <v>45639</v>
+        <v>45645</v>
       </c>
       <c r="C240" s="2">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -3777,10 +3777,10 @@
         <v>1</v>
       </c>
       <c r="B241" s="2">
-        <v>45641</v>
+        <v>45646</v>
       </c>
       <c r="C241" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D241" s="2" t="s">
         <v>5</v>
@@ -3791,10 +3791,10 @@
         <v>1</v>
       </c>
       <c r="B242" s="2">
-        <v>45642</v>
+        <v>45646</v>
       </c>
       <c r="C242" s="2">
-        <v>83</v>
+        <v>179</v>
       </c>
       <c r="D242" s="2" t="s">
         <v>7</v>
@@ -3805,13 +3805,13 @@
         <v>1</v>
       </c>
       <c r="B243" s="2">
-        <v>45644</v>
+        <v>45647</v>
       </c>
       <c r="C243" s="2">
-        <v>4</v>
+        <v>154</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -3819,10 +3819,10 @@
         <v>1</v>
       </c>
       <c r="B244" s="2">
-        <v>45644</v>
+        <v>45648</v>
       </c>
       <c r="C244" s="2">
-        <v>70</v>
+        <v>4</v>
       </c>
       <c r="D244" s="2" t="s">
         <v>5</v>
@@ -3833,10 +3833,10 @@
         <v>1</v>
       </c>
       <c r="B245" s="2">
-        <v>45645</v>
+        <v>45648</v>
       </c>
       <c r="C245" s="2">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="D245" s="2" t="s">
         <v>5</v>
@@ -3847,10 +3847,10 @@
         <v>1</v>
       </c>
       <c r="B246" s="2">
-        <v>45647</v>
+        <v>45649</v>
       </c>
       <c r="C246" s="2">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="D246" s="2" t="s">
         <v>5</v>
@@ -3861,13 +3861,13 @@
         <v>1</v>
       </c>
       <c r="B247" s="2">
-        <v>45648</v>
+        <v>45650</v>
       </c>
       <c r="C247" s="2">
-        <v>2</v>
+        <v>283</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -3875,10 +3875,10 @@
         <v>1</v>
       </c>
       <c r="B248" s="2">
-        <v>45648</v>
+        <v>45651</v>
       </c>
       <c r="C248" s="2">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="D248" s="2" t="s">
         <v>5</v>
@@ -3889,10 +3889,10 @@
         <v>1</v>
       </c>
       <c r="B249" s="2">
-        <v>45650</v>
+        <v>45652</v>
       </c>
       <c r="C249" s="2">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="D249" s="2" t="s">
         <v>5</v>
@@ -3903,13 +3903,13 @@
         <v>1</v>
       </c>
       <c r="B250" s="2">
-        <v>45651</v>
+        <v>45652</v>
       </c>
       <c r="C250" s="2">
-        <v>532</v>
+        <v>1</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -3917,13 +3917,13 @@
         <v>1</v>
       </c>
       <c r="B251" s="2">
-        <v>45652</v>
+        <v>45653</v>
       </c>
       <c r="C251" s="2">
+        <v>18</v>
+      </c>
+      <c r="D251" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="D251" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -3931,10 +3931,10 @@
         <v>1</v>
       </c>
       <c r="B252" s="2">
-        <v>45653</v>
+        <v>45654</v>
       </c>
       <c r="C252" s="2">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D252" s="2" t="s">
         <v>5</v>
@@ -3948,10 +3948,10 @@
         <v>45654</v>
       </c>
       <c r="C253" s="2">
-        <v>239</v>
+        <v>663</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -3962,7 +3962,7 @@
         <v>45655</v>
       </c>
       <c r="C254" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D254" s="2" t="s">
         <v>5</v>
@@ -3973,13 +3973,13 @@
         <v>1</v>
       </c>
       <c r="B255" s="2">
-        <v>45605</v>
+        <v>45656</v>
       </c>
       <c r="C255" s="2">
-        <v>187</v>
+        <v>4</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -3987,13 +3987,13 @@
         <v>1</v>
       </c>
       <c r="B256" s="2">
-        <v>45606</v>
+        <v>45656</v>
       </c>
       <c r="C256" s="2">
-        <v>29</v>
+        <v>272</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -4001,13 +4001,13 @@
         <v>1</v>
       </c>
       <c r="B257" s="2">
-        <v>45607</v>
+        <v>45605</v>
       </c>
       <c r="C257" s="2">
-        <v>3</v>
+        <v>187</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -4015,13 +4015,13 @@
         <v>1</v>
       </c>
       <c r="B258" s="2">
-        <v>45608</v>
+        <v>45606</v>
       </c>
       <c r="C258" s="2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -4029,10 +4029,10 @@
         <v>1</v>
       </c>
       <c r="B259" s="2">
-        <v>45609</v>
+        <v>45607</v>
       </c>
       <c r="C259" s="2">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="D259" s="2" t="s">
         <v>5</v>
@@ -4043,13 +4043,13 @@
         <v>1</v>
       </c>
       <c r="B260" s="2">
-        <v>45609</v>
+        <v>45608</v>
       </c>
       <c r="C260" s="2">
-        <v>319</v>
+        <v>32</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -4057,13 +4057,13 @@
         <v>1</v>
       </c>
       <c r="B261" s="2">
-        <v>45611</v>
+        <v>45609</v>
       </c>
       <c r="C261" s="2">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -4071,10 +4071,10 @@
         <v>1</v>
       </c>
       <c r="B262" s="2">
-        <v>45612</v>
+        <v>45609</v>
       </c>
       <c r="C262" s="2">
-        <v>37</v>
+        <v>319</v>
       </c>
       <c r="D262" s="2" t="s">
         <v>5</v>
@@ -4085,13 +4085,13 @@
         <v>1</v>
       </c>
       <c r="B263" s="2">
-        <v>45612</v>
+        <v>45611</v>
       </c>
       <c r="C263" s="2">
-        <v>614</v>
+        <v>0</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -4099,10 +4099,10 @@
         <v>1</v>
       </c>
       <c r="B264" s="2">
-        <v>45614</v>
+        <v>45612</v>
       </c>
       <c r="C264" s="2">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="D264" s="2" t="s">
         <v>5</v>
@@ -4113,10 +4113,10 @@
         <v>1</v>
       </c>
       <c r="B265" s="2">
-        <v>45615</v>
+        <v>45612</v>
       </c>
       <c r="C265" s="2">
-        <v>247</v>
+        <v>614</v>
       </c>
       <c r="D265" s="2" t="s">
         <v>5</v>
@@ -4127,10 +4127,10 @@
         <v>1</v>
       </c>
       <c r="B266" s="2">
-        <v>45617</v>
+        <v>45614</v>
       </c>
       <c r="C266" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D266" s="2" t="s">
         <v>5</v>
@@ -4141,13 +4141,13 @@
         <v>1</v>
       </c>
       <c r="B267" s="2">
-        <v>45620</v>
+        <v>45615</v>
       </c>
       <c r="C267" s="2">
-        <v>681</v>
+        <v>247</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -4155,10 +4155,10 @@
         <v>1</v>
       </c>
       <c r="B268" s="2">
-        <v>45620</v>
+        <v>45617</v>
       </c>
       <c r="C268" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D268" s="2" t="s">
         <v>5</v>
@@ -4169,10 +4169,10 @@
         <v>1</v>
       </c>
       <c r="B269" s="2">
-        <v>45623</v>
+        <v>45620</v>
       </c>
       <c r="C269" s="2">
-        <v>802</v>
+        <v>681</v>
       </c>
       <c r="D269" s="2" t="s">
         <v>6</v>
@@ -4183,13 +4183,13 @@
         <v>1</v>
       </c>
       <c r="B270" s="2">
-        <v>45624</v>
+        <v>45620</v>
       </c>
       <c r="C270" s="2">
-        <v>156</v>
+        <v>1</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -4197,10 +4197,10 @@
         <v>1</v>
       </c>
       <c r="B271" s="2">
-        <v>45626</v>
+        <v>45623</v>
       </c>
       <c r="C271" s="2">
-        <v>785</v>
+        <v>802</v>
       </c>
       <c r="D271" s="2" t="s">
         <v>6</v>
@@ -4211,13 +4211,13 @@
         <v>1</v>
       </c>
       <c r="B272" s="2">
-        <v>45627</v>
+        <v>45624</v>
       </c>
       <c r="C272" s="2">
-        <v>3</v>
+        <v>156</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -4225,13 +4225,13 @@
         <v>1</v>
       </c>
       <c r="B273" s="2">
-        <v>45627</v>
+        <v>45626</v>
       </c>
       <c r="C273" s="2">
-        <v>109</v>
+        <v>785</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -4239,10 +4239,10 @@
         <v>1</v>
       </c>
       <c r="B274" s="2">
-        <v>45629</v>
+        <v>45627</v>
       </c>
       <c r="C274" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D274" s="2" t="s">
         <v>5</v>
@@ -4253,13 +4253,13 @@
         <v>1</v>
       </c>
       <c r="B275" s="2">
-        <v>45629</v>
+        <v>45627</v>
       </c>
       <c r="C275" s="2">
-        <v>455</v>
+        <v>109</v>
       </c>
       <c r="D275" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -4267,7 +4267,7 @@
         <v>1</v>
       </c>
       <c r="B276" s="2">
-        <v>45630</v>
+        <v>45629</v>
       </c>
       <c r="C276" s="2">
         <v>1</v>
@@ -4281,13 +4281,13 @@
         <v>1</v>
       </c>
       <c r="B277" s="2">
-        <v>45630</v>
+        <v>45629</v>
       </c>
       <c r="C277" s="2">
-        <v>34</v>
+        <v>455</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -4295,13 +4295,13 @@
         <v>1</v>
       </c>
       <c r="B278" s="2">
-        <v>45631</v>
+        <v>45630</v>
       </c>
       <c r="C278" s="2">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -4309,13 +4309,13 @@
         <v>1</v>
       </c>
       <c r="B279" s="2">
-        <v>45632</v>
+        <v>45630</v>
       </c>
       <c r="C279" s="2">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -4323,13 +4323,13 @@
         <v>1</v>
       </c>
       <c r="B280" s="2">
-        <v>45633</v>
+        <v>45631</v>
       </c>
       <c r="C280" s="2">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -4337,13 +4337,13 @@
         <v>1</v>
       </c>
       <c r="B281" s="2">
-        <v>45634</v>
+        <v>45632</v>
       </c>
       <c r="C281" s="2">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -4351,10 +4351,10 @@
         <v>1</v>
       </c>
       <c r="B282" s="2">
-        <v>45635</v>
+        <v>45633</v>
       </c>
       <c r="C282" s="2">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="D282" s="2" t="s">
         <v>5</v>
@@ -4365,13 +4365,13 @@
         <v>1</v>
       </c>
       <c r="B283" s="2">
-        <v>45636</v>
+        <v>45634</v>
       </c>
       <c r="C283" s="2">
-        <v>4</v>
+        <v>108</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -4379,13 +4379,13 @@
         <v>1</v>
       </c>
       <c r="B284" s="2">
-        <v>45637</v>
+        <v>45635</v>
       </c>
       <c r="C284" s="2">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -4393,10 +4393,10 @@
         <v>1</v>
       </c>
       <c r="B285" s="2">
-        <v>45638</v>
+        <v>45636</v>
       </c>
       <c r="C285" s="2">
-        <v>66</v>
+        <v>4</v>
       </c>
       <c r="D285" s="2" t="s">
         <v>5</v>
@@ -4407,13 +4407,13 @@
         <v>1</v>
       </c>
       <c r="B286" s="2">
-        <v>45638</v>
+        <v>45637</v>
       </c>
       <c r="C286" s="2">
-        <v>514</v>
+        <v>28</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -4421,10 +4421,10 @@
         <v>1</v>
       </c>
       <c r="B287" s="2">
-        <v>45640</v>
+        <v>45638</v>
       </c>
       <c r="C287" s="2">
-        <v>9</v>
+        <v>66</v>
       </c>
       <c r="D287" s="2" t="s">
         <v>5</v>
@@ -4435,13 +4435,13 @@
         <v>1</v>
       </c>
       <c r="B288" s="2">
-        <v>45640</v>
+        <v>45638</v>
       </c>
       <c r="C288" s="2">
-        <v>166</v>
+        <v>514</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -4449,10 +4449,10 @@
         <v>1</v>
       </c>
       <c r="B289" s="2">
-        <v>45641</v>
+        <v>45640</v>
       </c>
       <c r="C289" s="2">
-        <v>74</v>
+        <v>9</v>
       </c>
       <c r="D289" s="2" t="s">
         <v>5</v>
@@ -4463,13 +4463,13 @@
         <v>1</v>
       </c>
       <c r="B290" s="2">
-        <v>45641</v>
+        <v>45640</v>
       </c>
       <c r="C290" s="2">
-        <v>802</v>
+        <v>166</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -4477,10 +4477,10 @@
         <v>1</v>
       </c>
       <c r="B291" s="2">
-        <v>45643</v>
+        <v>45641</v>
       </c>
       <c r="C291" s="2">
-        <v>8</v>
+        <v>74</v>
       </c>
       <c r="D291" s="2" t="s">
         <v>5</v>
@@ -4491,10 +4491,10 @@
         <v>1</v>
       </c>
       <c r="B292" s="2">
-        <v>45644</v>
+        <v>45641</v>
       </c>
       <c r="C292" s="2">
-        <v>547</v>
+        <v>802</v>
       </c>
       <c r="D292" s="2" t="s">
         <v>5</v>
@@ -4505,10 +4505,10 @@
         <v>1</v>
       </c>
       <c r="B293" s="2">
-        <v>45646</v>
+        <v>45643</v>
       </c>
       <c r="C293" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D293" s="2" t="s">
         <v>5</v>
@@ -4519,10 +4519,10 @@
         <v>1</v>
       </c>
       <c r="B294" s="2">
-        <v>45646</v>
+        <v>45644</v>
       </c>
       <c r="C294" s="2">
-        <v>2</v>
+        <v>547</v>
       </c>
       <c r="D294" s="2" t="s">
         <v>5</v>
@@ -4533,10 +4533,10 @@
         <v>1</v>
       </c>
       <c r="B295" s="2">
-        <v>45647</v>
+        <v>45646</v>
       </c>
       <c r="C295" s="2">
-        <v>890</v>
+        <v>7</v>
       </c>
       <c r="D295" s="2" t="s">
         <v>5</v>
@@ -4547,10 +4547,10 @@
         <v>1</v>
       </c>
       <c r="B296" s="2">
-        <v>45649</v>
+        <v>45646</v>
       </c>
       <c r="C296" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D296" s="2" t="s">
         <v>5</v>
@@ -4561,13 +4561,13 @@
         <v>1</v>
       </c>
       <c r="B297" s="2">
-        <v>45649</v>
+        <v>45647</v>
       </c>
       <c r="C297" s="2">
-        <v>1266</v>
+        <v>890</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -4578,7 +4578,7 @@
         <v>45649</v>
       </c>
       <c r="C298" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D298" s="2" t="s">
         <v>5</v>
@@ -4589,10 +4589,10 @@
         <v>1</v>
       </c>
       <c r="B299" s="2">
-        <v>45652</v>
+        <v>45649</v>
       </c>
       <c r="C299" s="2">
-        <v>1873</v>
+        <v>1266</v>
       </c>
       <c r="D299" s="2" t="s">
         <v>6</v>
@@ -4603,13 +4603,13 @@
         <v>1</v>
       </c>
       <c r="B300" s="2">
-        <v>45653</v>
+        <v>45649</v>
       </c>
       <c r="C300" s="2">
-        <v>455</v>
+        <v>1</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -4617,13 +4617,13 @@
         <v>1</v>
       </c>
       <c r="B301" s="2">
-        <v>45655</v>
+        <v>45652</v>
       </c>
       <c r="C301" s="2">
-        <v>7</v>
+        <v>1873</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -4631,13 +4631,13 @@
         <v>1</v>
       </c>
       <c r="B302" s="2">
-        <v>45655</v>
+        <v>45653</v>
       </c>
       <c r="C302" s="2">
-        <v>1575</v>
+        <v>455</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -4645,13 +4645,13 @@
         <v>1</v>
       </c>
       <c r="B303" s="2">
-        <v>45656</v>
+        <v>45655</v>
       </c>
       <c r="C303" s="2">
-        <v>546</v>
+        <v>7</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -4659,13 +4659,13 @@
         <v>1</v>
       </c>
       <c r="B304" s="2">
-        <v>45605</v>
+        <v>45655</v>
       </c>
       <c r="C304" s="2">
-        <v>17</v>
+        <v>1575</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -4673,13 +4673,13 @@
         <v>1</v>
       </c>
       <c r="B305" s="2">
-        <v>45606</v>
+        <v>45656</v>
       </c>
       <c r="C305" s="2">
-        <v>211</v>
+        <v>546</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -4687,10 +4687,10 @@
         <v>1</v>
       </c>
       <c r="B306" s="2">
-        <v>45607</v>
+        <v>45604</v>
       </c>
       <c r="C306" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D306" s="2" t="s">
         <v>5</v>
@@ -4701,10 +4701,10 @@
         <v>1</v>
       </c>
       <c r="B307" s="2">
-        <v>45608</v>
+        <v>45606</v>
       </c>
       <c r="C307" s="2">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D307" s="2" t="s">
         <v>5</v>
@@ -4715,13 +4715,13 @@
         <v>1</v>
       </c>
       <c r="B308" s="2">
-        <v>45609</v>
+        <v>45606</v>
       </c>
       <c r="C308" s="2">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -4729,13 +4729,13 @@
         <v>1</v>
       </c>
       <c r="B309" s="2">
-        <v>45610</v>
+        <v>45609</v>
       </c>
       <c r="C309" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D309" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -4746,10 +4746,10 @@
         <v>45610</v>
       </c>
       <c r="C310" s="2">
-        <v>237</v>
+        <v>28</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -4760,10 +4760,10 @@
         <v>45612</v>
       </c>
       <c r="C311" s="2">
-        <v>208</v>
+        <v>456</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -4774,10 +4774,10 @@
         <v>45613</v>
       </c>
       <c r="C312" s="2">
-        <v>3</v>
+        <v>217</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -4785,10 +4785,10 @@
         <v>1</v>
       </c>
       <c r="B313" s="2">
-        <v>45613</v>
+        <v>45614</v>
       </c>
       <c r="C313" s="2">
-        <v>606</v>
+        <v>25</v>
       </c>
       <c r="D313" s="2" t="s">
         <v>5</v>
@@ -4799,13 +4799,13 @@
         <v>1</v>
       </c>
       <c r="B314" s="2">
-        <v>45615</v>
+        <v>45614</v>
       </c>
       <c r="C314" s="2">
-        <v>17</v>
+        <v>320</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -4813,13 +4813,13 @@
         <v>1</v>
       </c>
       <c r="B315" s="2">
-        <v>45616</v>
+        <v>45615</v>
       </c>
       <c r="C315" s="2">
-        <v>317</v>
+        <v>194</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -4830,10 +4830,10 @@
         <v>45616</v>
       </c>
       <c r="C316" s="2">
-        <v>202</v>
+        <v>1</v>
       </c>
       <c r="D316" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -4841,13 +4841,13 @@
         <v>1</v>
       </c>
       <c r="B317" s="2">
-        <v>45619</v>
+        <v>45616</v>
       </c>
       <c r="C317" s="2">
-        <v>779</v>
+        <v>35</v>
       </c>
       <c r="D317" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -4855,13 +4855,13 @@
         <v>1</v>
       </c>
       <c r="B318" s="2">
-        <v>45619</v>
+        <v>45617</v>
       </c>
       <c r="C318" s="2">
-        <v>719</v>
+        <v>27</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -4869,13 +4869,13 @@
         <v>1</v>
       </c>
       <c r="B319" s="2">
-        <v>45620</v>
+        <v>45617</v>
       </c>
       <c r="C319" s="2">
-        <v>55</v>
+        <v>272</v>
       </c>
       <c r="D319" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -4883,10 +4883,10 @@
         <v>1</v>
       </c>
       <c r="B320" s="2">
-        <v>45622</v>
+        <v>45618</v>
       </c>
       <c r="C320" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D320" s="2" t="s">
         <v>5</v>
@@ -4897,10 +4897,10 @@
         <v>1</v>
       </c>
       <c r="B321" s="2">
-        <v>45622</v>
+        <v>45618</v>
       </c>
       <c r="C321" s="2">
-        <v>560</v>
+        <v>482</v>
       </c>
       <c r="D321" s="2" t="s">
         <v>6</v>
@@ -4911,10 +4911,10 @@
         <v>1</v>
       </c>
       <c r="B322" s="2">
-        <v>45623</v>
+        <v>45619</v>
       </c>
       <c r="C322" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D322" s="2" t="s">
         <v>5</v>
@@ -4925,13 +4925,13 @@
         <v>1</v>
       </c>
       <c r="B323" s="2">
-        <v>45623</v>
+        <v>45620</v>
       </c>
       <c r="C323" s="2">
-        <v>126</v>
+        <v>43</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -4939,10 +4939,10 @@
         <v>1</v>
       </c>
       <c r="B324" s="2">
-        <v>45625</v>
+        <v>45620</v>
       </c>
       <c r="C324" s="2">
-        <v>3</v>
+        <v>670</v>
       </c>
       <c r="D324" s="2" t="s">
         <v>5</v>
@@ -4953,13 +4953,13 @@
         <v>1</v>
       </c>
       <c r="B325" s="2">
-        <v>45625</v>
+        <v>45621</v>
       </c>
       <c r="C325" s="2">
-        <v>1117</v>
+        <v>5</v>
       </c>
       <c r="D325" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -4967,13 +4967,13 @@
         <v>1</v>
       </c>
       <c r="B326" s="2">
-        <v>45626</v>
+        <v>45621</v>
       </c>
       <c r="C326" s="2">
-        <v>3</v>
+        <v>529</v>
       </c>
       <c r="D326" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -4981,13 +4981,13 @@
         <v>1</v>
       </c>
       <c r="B327" s="2">
-        <v>45626</v>
+        <v>45622</v>
       </c>
       <c r="C327" s="2">
-        <v>128</v>
+        <v>9</v>
       </c>
       <c r="D327" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -4995,10 +4995,10 @@
         <v>1</v>
       </c>
       <c r="B328" s="2">
-        <v>45628</v>
+        <v>45623</v>
       </c>
       <c r="C328" s="2">
-        <v>2</v>
+        <v>608</v>
       </c>
       <c r="D328" s="2" t="s">
         <v>5</v>
@@ -5009,10 +5009,10 @@
         <v>1</v>
       </c>
       <c r="B329" s="2">
-        <v>45628</v>
+        <v>45624</v>
       </c>
       <c r="C329" s="2">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="D329" s="2" t="s">
         <v>5</v>
@@ -5023,10 +5023,10 @@
         <v>1</v>
       </c>
       <c r="B330" s="2">
-        <v>45629</v>
+        <v>45625</v>
       </c>
       <c r="C330" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D330" s="2" t="s">
         <v>5</v>
@@ -5037,10 +5037,10 @@
         <v>1</v>
       </c>
       <c r="B331" s="2">
-        <v>45631</v>
+        <v>45625</v>
       </c>
       <c r="C331" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D331" s="2" t="s">
         <v>5</v>
@@ -5051,10 +5051,10 @@
         <v>1</v>
       </c>
       <c r="B332" s="2">
-        <v>45631</v>
+        <v>45627</v>
       </c>
       <c r="C332" s="2">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="D332" s="2" t="s">
         <v>5</v>
@@ -5065,13 +5065,13 @@
         <v>1</v>
       </c>
       <c r="B333" s="2">
-        <v>45634</v>
+        <v>45629</v>
       </c>
       <c r="C333" s="2">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="D333" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -5079,13 +5079,13 @@
         <v>1</v>
       </c>
       <c r="B334" s="2">
-        <v>45634</v>
+        <v>45632</v>
       </c>
       <c r="C334" s="2">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -5096,10 +5096,10 @@
         <v>45635</v>
       </c>
       <c r="C335" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D335" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -5107,13 +5107,13 @@
         <v>1</v>
       </c>
       <c r="B336" s="2">
-        <v>45636</v>
+        <v>45635</v>
       </c>
       <c r="C336" s="2">
-        <v>6</v>
+        <v>65</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -5121,13 +5121,13 @@
         <v>1</v>
       </c>
       <c r="B337" s="2">
-        <v>45637</v>
+        <v>45638</v>
       </c>
       <c r="C337" s="2">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -5135,10 +5135,10 @@
         <v>1</v>
       </c>
       <c r="B338" s="2">
-        <v>45638</v>
+        <v>45639</v>
       </c>
       <c r="C338" s="2">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="D338" s="2" t="s">
         <v>8</v>
@@ -5149,10 +5149,10 @@
         <v>1</v>
       </c>
       <c r="B339" s="2">
-        <v>45639</v>
+        <v>45640</v>
       </c>
       <c r="C339" s="2">
-        <v>7</v>
+        <v>56</v>
       </c>
       <c r="D339" s="2" t="s">
         <v>5</v>
@@ -5166,10 +5166,10 @@
         <v>45641</v>
       </c>
       <c r="C340" s="2">
-        <v>98</v>
+        <v>1165</v>
       </c>
       <c r="D340" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -5180,10 +5180,10 @@
         <v>45642</v>
       </c>
       <c r="C341" s="2">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D341" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -5191,10 +5191,10 @@
         <v>1</v>
       </c>
       <c r="B342" s="2">
-        <v>45642</v>
+        <v>45643</v>
       </c>
       <c r="C342" s="2">
-        <v>602</v>
+        <v>71</v>
       </c>
       <c r="D342" s="2" t="s">
         <v>5</v>
@@ -5208,10 +5208,10 @@
         <v>45644</v>
       </c>
       <c r="C343" s="2">
-        <v>75</v>
+        <v>1245</v>
       </c>
       <c r="D343" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -5222,10 +5222,10 @@
         <v>45645</v>
       </c>
       <c r="C344" s="2">
-        <v>2</v>
+        <v>81</v>
       </c>
       <c r="D344" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -5233,10 +5233,10 @@
         <v>1</v>
       </c>
       <c r="B345" s="2">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="C345" s="2">
-        <v>607</v>
+        <v>78</v>
       </c>
       <c r="D345" s="2" t="s">
         <v>5</v>
@@ -5247,13 +5247,13 @@
         <v>1</v>
       </c>
       <c r="B346" s="2">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="C346" s="2">
-        <v>1230</v>
+        <v>929</v>
       </c>
       <c r="D346" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -5261,10 +5261,10 @@
         <v>1</v>
       </c>
       <c r="B347" s="2">
-        <v>45648</v>
+        <v>45647</v>
       </c>
       <c r="C347" s="2">
-        <v>903</v>
+        <v>2</v>
       </c>
       <c r="D347" s="2" t="s">
         <v>5</v>
@@ -5275,10 +5275,10 @@
         <v>1</v>
       </c>
       <c r="B348" s="2">
-        <v>45648</v>
+        <v>45647</v>
       </c>
       <c r="C348" s="2">
-        <v>1613</v>
+        <v>1531</v>
       </c>
       <c r="D348" s="2" t="s">
         <v>6</v>
@@ -5289,13 +5289,13 @@
         <v>1</v>
       </c>
       <c r="B349" s="2">
-        <v>45649</v>
+        <v>45648</v>
       </c>
       <c r="C349" s="2">
-        <v>241</v>
+        <v>16</v>
       </c>
       <c r="D349" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -5303,13 +5303,13 @@
         <v>1</v>
       </c>
       <c r="B350" s="2">
-        <v>45650</v>
+        <v>45648</v>
       </c>
       <c r="C350" s="2">
-        <v>1</v>
+        <v>224</v>
       </c>
       <c r="D350" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -5317,10 +5317,10 @@
         <v>1</v>
       </c>
       <c r="B351" s="2">
-        <v>45651</v>
+        <v>45649</v>
       </c>
       <c r="C351" s="2">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="D351" s="2" t="s">
         <v>5</v>
@@ -5331,10 +5331,10 @@
         <v>1</v>
       </c>
       <c r="B352" s="2">
-        <v>45651</v>
+        <v>45649</v>
       </c>
       <c r="C352" s="2">
-        <v>830</v>
+        <v>1051</v>
       </c>
       <c r="D352" s="2" t="s">
         <v>5</v>
@@ -5345,13 +5345,13 @@
         <v>1</v>
       </c>
       <c r="B353" s="2">
-        <v>45651</v>
+        <v>45650</v>
       </c>
       <c r="C353" s="2">
-        <v>1321</v>
+        <v>7</v>
       </c>
       <c r="D353" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -5359,13 +5359,13 @@
         <v>1</v>
       </c>
       <c r="B354" s="2">
-        <v>45652</v>
+        <v>45650</v>
       </c>
       <c r="C354" s="2">
-        <v>384</v>
+        <v>1443</v>
       </c>
       <c r="D354" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -5373,10 +5373,10 @@
         <v>1</v>
       </c>
       <c r="B355" s="2">
-        <v>45654</v>
+        <v>45651</v>
       </c>
       <c r="C355" s="2">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D355" s="2" t="s">
         <v>5</v>
@@ -5387,13 +5387,13 @@
         <v>1</v>
       </c>
       <c r="B356" s="2">
-        <v>45654</v>
+        <v>45651</v>
       </c>
       <c r="C356" s="2">
-        <v>1825</v>
+        <v>1</v>
       </c>
       <c r="D356" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -5401,10 +5401,10 @@
         <v>1</v>
       </c>
       <c r="B357" s="2">
-        <v>45655</v>
+        <v>45652</v>
       </c>
       <c r="C357" s="2">
-        <v>1</v>
+        <v>837</v>
       </c>
       <c r="D357" s="2" t="s">
         <v>5</v>
@@ -5415,13 +5415,13 @@
         <v>1</v>
       </c>
       <c r="B358" s="2">
-        <v>45655</v>
+        <v>45653</v>
       </c>
       <c r="C358" s="2">
-        <v>493</v>
+        <v>1</v>
       </c>
       <c r="D358" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -5429,10 +5429,10 @@
         <v>1</v>
       </c>
       <c r="B359" s="2">
-        <v>45604</v>
+        <v>45654</v>
       </c>
       <c r="C359" s="2">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D359" s="2" t="s">
         <v>5</v>
@@ -5443,10 +5443,10 @@
         <v>1</v>
       </c>
       <c r="B360" s="2">
-        <v>45606</v>
+        <v>45655</v>
       </c>
       <c r="C360" s="2">
-        <v>1</v>
+        <v>646</v>
       </c>
       <c r="D360" s="2" t="s">
         <v>5</v>
@@ -5457,13 +5457,13 @@
         <v>1</v>
       </c>
       <c r="B361" s="2">
-        <v>45606</v>
+        <v>45656</v>
       </c>
       <c r="C361" s="2">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="D361" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -5471,13 +5471,13 @@
         <v>1</v>
       </c>
       <c r="B362" s="2">
-        <v>45609</v>
+        <v>45656</v>
       </c>
       <c r="C362" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D362" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -5485,13 +5485,13 @@
         <v>1</v>
       </c>
       <c r="B363" s="2">
-        <v>45610</v>
+        <v>45605</v>
       </c>
       <c r="C363" s="2">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="D363" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -5499,13 +5499,13 @@
         <v>1</v>
       </c>
       <c r="B364" s="2">
-        <v>45612</v>
+        <v>45605</v>
       </c>
       <c r="C364" s="2">
-        <v>456</v>
+        <v>18</v>
       </c>
       <c r="D364" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -5513,13 +5513,13 @@
         <v>1</v>
       </c>
       <c r="B365" s="2">
-        <v>45613</v>
+        <v>45607</v>
       </c>
       <c r="C365" s="2">
-        <v>217</v>
+        <v>27</v>
       </c>
       <c r="D365" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -5527,10 +5527,10 @@
         <v>1</v>
       </c>
       <c r="B366" s="2">
-        <v>45614</v>
+        <v>45608</v>
       </c>
       <c r="C366" s="2">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="D366" s="2" t="s">
         <v>5</v>
@@ -5541,13 +5541,13 @@
         <v>1</v>
       </c>
       <c r="B367" s="2">
-        <v>45614</v>
+        <v>45608</v>
       </c>
       <c r="C367" s="2">
-        <v>320</v>
+        <v>155</v>
       </c>
       <c r="D367" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -5555,13 +5555,13 @@
         <v>1</v>
       </c>
       <c r="B368" s="2">
-        <v>45615</v>
+        <v>45610</v>
       </c>
       <c r="C368" s="2">
-        <v>194</v>
+        <v>17</v>
       </c>
       <c r="D368" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -5569,13 +5569,13 @@
         <v>1</v>
       </c>
       <c r="B369" s="2">
-        <v>45616</v>
+        <v>45611</v>
       </c>
       <c r="C369" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D369" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -5583,13 +5583,13 @@
         <v>1</v>
       </c>
       <c r="B370" s="2">
-        <v>45616</v>
+        <v>45612</v>
       </c>
       <c r="C370" s="2">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="D370" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="371" spans="1:4">
@@ -5597,10 +5597,10 @@
         <v>1</v>
       </c>
       <c r="B371" s="2">
-        <v>45617</v>
+        <v>45613</v>
       </c>
       <c r="C371" s="2">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D371" s="2" t="s">
         <v>5</v>
@@ -5611,10 +5611,10 @@
         <v>1</v>
       </c>
       <c r="B372" s="2">
-        <v>45617</v>
+        <v>45614</v>
       </c>
       <c r="C372" s="2">
-        <v>272</v>
+        <v>2</v>
       </c>
       <c r="D372" s="2" t="s">
         <v>5</v>
@@ -5625,13 +5625,13 @@
         <v>1</v>
       </c>
       <c r="B373" s="2">
-        <v>45618</v>
+        <v>45614</v>
       </c>
       <c r="C373" s="2">
-        <v>2</v>
+        <v>236</v>
       </c>
       <c r="D373" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -5639,13 +5639,13 @@
         <v>1</v>
       </c>
       <c r="B374" s="2">
-        <v>45618</v>
+        <v>45614</v>
       </c>
       <c r="C374" s="2">
-        <v>482</v>
+        <v>45</v>
       </c>
       <c r="D374" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="375" spans="1:4">
@@ -5653,10 +5653,10 @@
         <v>1</v>
       </c>
       <c r="B375" s="2">
-        <v>45619</v>
+        <v>45616</v>
       </c>
       <c r="C375" s="2">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="D375" s="2" t="s">
         <v>5</v>
@@ -5667,10 +5667,10 @@
         <v>1</v>
       </c>
       <c r="B376" s="2">
-        <v>45620</v>
+        <v>45617</v>
       </c>
       <c r="C376" s="2">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="D376" s="2" t="s">
         <v>5</v>
@@ -5681,13 +5681,13 @@
         <v>1</v>
       </c>
       <c r="B377" s="2">
-        <v>45620</v>
+        <v>45617</v>
       </c>
       <c r="C377" s="2">
-        <v>670</v>
+        <v>209</v>
       </c>
       <c r="D377" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="378" spans="1:4">
@@ -5695,13 +5695,13 @@
         <v>1</v>
       </c>
       <c r="B378" s="2">
-        <v>45621</v>
+        <v>45617</v>
       </c>
       <c r="C378" s="2">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="D378" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="379" spans="1:4">
@@ -5709,13 +5709,13 @@
         <v>1</v>
       </c>
       <c r="B379" s="2">
-        <v>45621</v>
+        <v>45618</v>
       </c>
       <c r="C379" s="2">
-        <v>529</v>
+        <v>8</v>
       </c>
       <c r="D379" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="380" spans="1:4">
@@ -5723,10 +5723,10 @@
         <v>1</v>
       </c>
       <c r="B380" s="2">
-        <v>45622</v>
+        <v>45618</v>
       </c>
       <c r="C380" s="2">
-        <v>9</v>
+        <v>770</v>
       </c>
       <c r="D380" s="2" t="s">
         <v>5</v>
@@ -5737,13 +5737,13 @@
         <v>1</v>
       </c>
       <c r="B381" s="2">
-        <v>45623</v>
+        <v>45620</v>
       </c>
       <c r="C381" s="2">
-        <v>608</v>
+        <v>298</v>
       </c>
       <c r="D381" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="382" spans="1:4">
@@ -5751,10 +5751,10 @@
         <v>1</v>
       </c>
       <c r="B382" s="2">
-        <v>45624</v>
+        <v>45621</v>
       </c>
       <c r="C382" s="2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D382" s="2" t="s">
         <v>5</v>
@@ -5765,10 +5765,10 @@
         <v>1</v>
       </c>
       <c r="B383" s="2">
-        <v>45625</v>
+        <v>45621</v>
       </c>
       <c r="C383" s="2">
-        <v>9</v>
+        <v>480</v>
       </c>
       <c r="D383" s="2" t="s">
         <v>5</v>
@@ -5779,7 +5779,7 @@
         <v>1</v>
       </c>
       <c r="B384" s="2">
-        <v>45625</v>
+        <v>45623</v>
       </c>
       <c r="C384" s="2">
         <v>1</v>
@@ -5793,10 +5793,10 @@
         <v>1</v>
       </c>
       <c r="B385" s="2">
-        <v>45627</v>
+        <v>45624</v>
       </c>
       <c r="C385" s="2">
-        <v>1</v>
+        <v>583</v>
       </c>
       <c r="D385" s="2" t="s">
         <v>5</v>
@@ -5807,13 +5807,13 @@
         <v>1</v>
       </c>
       <c r="B386" s="2">
-        <v>45629</v>
+        <v>45627</v>
       </c>
       <c r="C386" s="2">
-        <v>31</v>
+        <v>637</v>
       </c>
       <c r="D386" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="387" spans="1:4">
@@ -5821,10 +5821,10 @@
         <v>1</v>
       </c>
       <c r="B387" s="2">
-        <v>45632</v>
+        <v>45628</v>
       </c>
       <c r="C387" s="2">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D387" s="2" t="s">
         <v>7</v>
@@ -5835,13 +5835,13 @@
         <v>1</v>
       </c>
       <c r="B388" s="2">
-        <v>45635</v>
+        <v>45631</v>
       </c>
       <c r="C388" s="2">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="D388" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="389" spans="1:4">
@@ -5849,13 +5849,13 @@
         <v>1</v>
       </c>
       <c r="B389" s="2">
-        <v>45635</v>
+        <v>45634</v>
       </c>
       <c r="C389" s="2">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="D389" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="390" spans="1:4">
@@ -5863,10 +5863,10 @@
         <v>1</v>
       </c>
       <c r="B390" s="2">
-        <v>45638</v>
+        <v>45634</v>
       </c>
       <c r="C390" s="2">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="D390" s="2" t="s">
         <v>7</v>
@@ -5877,13 +5877,13 @@
         <v>1</v>
       </c>
       <c r="B391" s="2">
-        <v>45639</v>
+        <v>45636</v>
       </c>
       <c r="C391" s="2">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="D391" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="392" spans="1:4">
@@ -5891,10 +5891,10 @@
         <v>1</v>
       </c>
       <c r="B392" s="2">
-        <v>45640</v>
+        <v>45637</v>
       </c>
       <c r="C392" s="2">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="D392" s="2" t="s">
         <v>5</v>
@@ -5905,10 +5905,10 @@
         <v>1</v>
       </c>
       <c r="B393" s="2">
-        <v>45641</v>
+        <v>45637</v>
       </c>
       <c r="C393" s="2">
-        <v>1165</v>
+        <v>778</v>
       </c>
       <c r="D393" s="2" t="s">
         <v>6</v>
@@ -5919,13 +5919,13 @@
         <v>1</v>
       </c>
       <c r="B394" s="2">
-        <v>45642</v>
+        <v>45639</v>
       </c>
       <c r="C394" s="2">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="D394" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="395" spans="1:4">
@@ -5933,10 +5933,10 @@
         <v>1</v>
       </c>
       <c r="B395" s="2">
-        <v>45643</v>
+        <v>45640</v>
       </c>
       <c r="C395" s="2">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="D395" s="2" t="s">
         <v>5</v>
@@ -5947,13 +5947,13 @@
         <v>1</v>
       </c>
       <c r="B396" s="2">
-        <v>45644</v>
+        <v>45640</v>
       </c>
       <c r="C396" s="2">
-        <v>1245</v>
+        <v>1</v>
       </c>
       <c r="D396" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="397" spans="1:4">
@@ -5961,13 +5961,13 @@
         <v>1</v>
       </c>
       <c r="B397" s="2">
-        <v>45645</v>
+        <v>45640</v>
       </c>
       <c r="C397" s="2">
-        <v>81</v>
+        <v>1649</v>
       </c>
       <c r="D397" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="398" spans="1:4">
@@ -5975,10 +5975,10 @@
         <v>1</v>
       </c>
       <c r="B398" s="2">
-        <v>45646</v>
+        <v>45642</v>
       </c>
       <c r="C398" s="2">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D398" s="2" t="s">
         <v>5</v>
@@ -5989,13 +5989,13 @@
         <v>1</v>
       </c>
       <c r="B399" s="2">
-        <v>45646</v>
+        <v>45643</v>
       </c>
       <c r="C399" s="2">
-        <v>929</v>
+        <v>1155</v>
       </c>
       <c r="D399" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="400" spans="1:4">
@@ -6003,13 +6003,13 @@
         <v>1</v>
       </c>
       <c r="B400" s="2">
-        <v>45647</v>
+        <v>45643</v>
       </c>
       <c r="C400" s="2">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="D400" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="401" spans="1:4">
@@ -6017,13 +6017,13 @@
         <v>1</v>
       </c>
       <c r="B401" s="2">
-        <v>45647</v>
+        <v>45644</v>
       </c>
       <c r="C401" s="2">
-        <v>1531</v>
+        <v>2</v>
       </c>
       <c r="D401" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="402" spans="1:4">
@@ -6031,10 +6031,10 @@
         <v>1</v>
       </c>
       <c r="B402" s="2">
-        <v>45648</v>
+        <v>45645</v>
       </c>
       <c r="C402" s="2">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="D402" s="2" t="s">
         <v>5</v>
@@ -6045,13 +6045,13 @@
         <v>1</v>
       </c>
       <c r="B403" s="2">
-        <v>45648</v>
+        <v>45646</v>
       </c>
       <c r="C403" s="2">
-        <v>224</v>
+        <v>3</v>
       </c>
       <c r="D403" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="404" spans="1:4">
@@ -6059,13 +6059,13 @@
         <v>1</v>
       </c>
       <c r="B404" s="2">
-        <v>45649</v>
+        <v>45646</v>
       </c>
       <c r="C404" s="2">
-        <v>57</v>
+        <v>936</v>
       </c>
       <c r="D404" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="405" spans="1:4">
@@ -6073,13 +6073,13 @@
         <v>1</v>
       </c>
       <c r="B405" s="2">
-        <v>45649</v>
+        <v>45646</v>
       </c>
       <c r="C405" s="2">
-        <v>1051</v>
+        <v>117</v>
       </c>
       <c r="D405" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="406" spans="1:4">
@@ -6087,10 +6087,10 @@
         <v>1</v>
       </c>
       <c r="B406" s="2">
-        <v>45650</v>
+        <v>45647</v>
       </c>
       <c r="C406" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D406" s="2" t="s">
         <v>5</v>
@@ -6101,13 +6101,13 @@
         <v>1</v>
       </c>
       <c r="B407" s="2">
-        <v>45650</v>
+        <v>45649</v>
       </c>
       <c r="C407" s="2">
-        <v>1443</v>
+        <v>3</v>
       </c>
       <c r="D407" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="408" spans="1:4">
@@ -6115,13 +6115,13 @@
         <v>1</v>
       </c>
       <c r="B408" s="2">
-        <v>45651</v>
+        <v>45649</v>
       </c>
       <c r="C408" s="2">
-        <v>20</v>
+        <v>138</v>
       </c>
       <c r="D408" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="409" spans="1:4">
@@ -6129,10 +6129,10 @@
         <v>1</v>
       </c>
       <c r="B409" s="2">
-        <v>45651</v>
+        <v>45650</v>
       </c>
       <c r="C409" s="2">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D409" s="2" t="s">
         <v>5</v>
@@ -6143,10 +6143,10 @@
         <v>1</v>
       </c>
       <c r="B410" s="2">
-        <v>45652</v>
+        <v>45650</v>
       </c>
       <c r="C410" s="2">
-        <v>837</v>
+        <v>766</v>
       </c>
       <c r="D410" s="2" t="s">
         <v>5</v>
@@ -6157,7 +6157,7 @@
         <v>1</v>
       </c>
       <c r="B411" s="2">
-        <v>45653</v>
+        <v>45652</v>
       </c>
       <c r="C411" s="2">
         <v>1</v>
@@ -6171,13 +6171,13 @@
         <v>1</v>
       </c>
       <c r="B412" s="2">
-        <v>45654</v>
+        <v>45652</v>
       </c>
       <c r="C412" s="2">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D412" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="413" spans="1:4">
@@ -6185,10 +6185,10 @@
         <v>1</v>
       </c>
       <c r="B413" s="2">
-        <v>45655</v>
+        <v>45653</v>
       </c>
       <c r="C413" s="2">
-        <v>646</v>
+        <v>6</v>
       </c>
       <c r="D413" s="2" t="s">
         <v>5</v>
@@ -6199,10 +6199,10 @@
         <v>1</v>
       </c>
       <c r="B414" s="2">
-        <v>45656</v>
+        <v>45653</v>
       </c>
       <c r="C414" s="2">
-        <v>7</v>
+        <v>533</v>
       </c>
       <c r="D414" s="2" t="s">
         <v>5</v>
@@ -6216,7 +6216,7 @@
         <v>45656</v>
       </c>
       <c r="C415" s="2">
-        <v>2</v>
+        <v>633</v>
       </c>
       <c r="D415" s="2" t="s">
         <v>5</v>
